--- a/docs/d/107/inyear.xlsx
+++ b/docs/d/107/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" s="9" t="n">
         <v>0</v>
@@ -3102,7 +3102,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -3148,8 +3148,8 @@
       <c r="Q24" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R24" s="9" t="n">
-        <v>1</v>
+      <c r="R24" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S24" s="9" t="n">
         <v>0</v>
@@ -5768,7 +5768,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5820,8 +5820,8 @@
       <c r="S50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T50" s="9" t="n">
-        <v>0</v>
+      <c r="T50" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U50" s="9" t="n">
         <v>0</v>
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8159,8 +8159,8 @@
       <c r="S73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T73" s="9" t="n">
-        <v>0</v>
+      <c r="T73" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U73" s="9" t="n">
         <v>0</v>
@@ -10588,13 +10588,13 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -10753,7 +10753,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -10918,7 +10918,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>

--- a/docs/d/107/inyear.xlsx
+++ b/docs/d/107/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,11 @@
       <c r="AB5" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC5" s="4" t="inlineStr"/>
+      <c r="AC5" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -2777,7 +2781,11 @@
       <c r="AB20" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC20" s="4" t="inlineStr"/>
+      <c r="AC20" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -2878,7 +2886,11 @@
       <c r="AB21" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC21" s="4" t="inlineStr"/>
+      <c r="AC21" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -2979,7 +2991,11 @@
       <c r="AB22" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC22" s="4" t="inlineStr"/>
+      <c r="AC22" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -3181,7 +3197,11 @@
       <c r="AB24" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC24" s="4" t="inlineStr"/>
+      <c r="AC24" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -3282,7 +3302,11 @@
       <c r="AB25" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC25" s="4" t="inlineStr"/>
+      <c r="AC25" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -3488,7 +3512,11 @@
       <c r="AB27" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC27" s="4" t="inlineStr"/>
+      <c r="AC27" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -4312,7 +4340,11 @@
       <c r="AB35" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC35" s="4" t="inlineStr"/>
+      <c r="AC35" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -4833,7 +4865,11 @@
       <c r="AB40" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC40" s="4" t="inlineStr"/>
+      <c r="AC40" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -4934,7 +4970,11 @@
       <c r="AB41" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC41" s="4" t="inlineStr"/>
+      <c r="AC41" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -5136,7 +5176,11 @@
       <c r="AB43" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC43" s="4" t="inlineStr"/>
+      <c r="AC43" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -5338,7 +5382,11 @@
       <c r="AB45" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC45" s="4" t="inlineStr"/>
+      <c r="AC45" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -5746,7 +5794,11 @@
       <c r="AB49" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC49" s="4" t="inlineStr"/>
+      <c r="AC49" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -6150,7 +6202,11 @@
       <c r="AB53" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC53" s="4" t="inlineStr"/>
+      <c r="AC53" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -6760,7 +6816,11 @@
       <c r="AB59" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC59" s="4" t="inlineStr"/>
+      <c r="AC59" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -6861,7 +6921,11 @@
       <c r="AB60" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC60" s="4" t="inlineStr"/>
+      <c r="AC60" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -6962,7 +7026,11 @@
       <c r="AB61" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC61" s="4" t="inlineStr"/>
+      <c r="AC61" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -7168,7 +7236,11 @@
       <c r="AB63" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC63" s="4" t="inlineStr"/>
+      <c r="AC63" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -7370,7 +7442,11 @@
       <c r="AB65" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC65" s="4" t="inlineStr"/>
+      <c r="AC65" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -8186,7 +8262,11 @@
       <c r="AB73" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC73" s="4" t="inlineStr"/>
+      <c r="AC73" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -9222,7 +9302,11 @@
       <c r="AB83" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC83" s="4" t="inlineStr"/>
+      <c r="AC83" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -9323,7 +9407,11 @@
       <c r="AB84" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC84" s="4" t="inlineStr"/>
+      <c r="AC84" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -9424,7 +9512,11 @@
       <c r="AB85" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC85" s="4" t="inlineStr"/>
+      <c r="AC85" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -9626,7 +9718,11 @@
       <c r="AB87" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC87" s="4" t="inlineStr"/>
+      <c r="AC87" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
@@ -9828,7 +9924,11 @@
       <c r="AB89" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC89" s="4" t="inlineStr"/>
+      <c r="AC89" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">

--- a/docs/d/107/inyear.xlsx
+++ b/docs/d/107/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 13 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 13 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 43 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 37 clubs short</t>
         </is>
       </c>
     </row>
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -2049,8 +2049,8 @@
       <c r="Y13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z13" s="9" t="n">
-        <v>0</v>
+      <c r="Z13" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA13" s="10" t="n">
         <v>1</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2457,8 +2457,8 @@
       <c r="Y17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z17" s="9" t="n">
-        <v>0</v>
+      <c r="Z17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA17" s="10" t="n">
         <v>1</v>
@@ -2611,13 +2611,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>0</v>
       </c>
       <c r="V19" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0</v>
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="P25" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q25" s="9" t="n">
         <v>1</v>
@@ -5202,7 +5202,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -5272,8 +5272,8 @@
       <c r="Y44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z44" s="9" t="n">
-        <v>0</v>
+      <c r="Z44" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA44" s="10" t="n">
         <v>1</v>
@@ -6022,7 +6022,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -6074,8 +6074,8 @@
       <c r="S52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T52" s="9" t="n">
-        <v>0</v>
+      <c r="T52" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U52" s="9" t="n">
         <v>0</v>
@@ -7201,7 +7201,7 @@
         <v>0</v>
       </c>
       <c r="Q63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R63" s="9" t="n">
         <v>0</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="P68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q68" s="9" t="n">
         <v>0</v>
@@ -8809,7 +8809,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8879,8 +8879,8 @@
       <c r="Y79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z79" s="9" t="n">
-        <v>0</v>
+      <c r="Z79" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA79" s="10" t="n">
         <v>1</v>
@@ -8958,7 +8958,7 @@
         <v>2</v>
       </c>
       <c r="Q80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R80" s="9" t="n">
         <v>0</v>
@@ -9124,7 +9124,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -9194,8 +9194,8 @@
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="9" t="n">
-        <v>0</v>
+      <c r="Z82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA82" s="10" t="n">
         <v>1</v>
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9342,13 +9342,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
@@ -9386,11 +9386,11 @@
       <c r="U84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V84" s="9" t="n">
-        <v>2</v>
+      <c r="V84" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W84" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X84" s="10" t="n">
         <v>7</v>
@@ -9950,7 +9950,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -10020,8 +10020,8 @@
       <c r="Y90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z90" s="9" t="n">
-        <v>0</v>
+      <c r="Z90" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA90" s="10" t="n">
         <v>1</v>
@@ -10589,7 +10589,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -10622,7 +10622,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -10820,7 +10820,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -10886,7 +10886,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -11084,7 +11084,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -11117,7 +11117,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -11183,7 +11183,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>

--- a/docs/d/107/inyear.xlsx
+++ b/docs/d/107/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$96</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 13 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 13 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 37 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 22 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC94"/>
+  <dimension ref="A1:AC96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1516,7 +1516,7 @@
         <v>0</v>
       </c>
       <c r="S8" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" s="9" t="n">
         <v>0</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="P22" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q22" s="9" t="n">
         <v>0</v>
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3278,8 +3278,8 @@
       <c r="T25" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U25" s="9" t="n">
-        <v>0</v>
+      <c r="U25" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V25" s="9" t="n">
         <v>1</v>
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3342,13 +3342,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>0</v>
       </c>
       <c r="S26" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26" s="9" t="n">
         <v>0</v>
@@ -3387,7 +3387,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
@@ -3398,8 +3398,8 @@
       <c r="Y26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z26" s="9" t="n">
-        <v>0</v>
+      <c r="Z26" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA26" s="10" t="n">
         <v>1</v>
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3713,8 +3713,8 @@
       <c r="Y29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z29" s="9" t="n">
-        <v>0</v>
+      <c r="Z29" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA29" s="10" t="n">
         <v>1</v>
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3923,8 +3923,8 @@
       <c r="Y31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z31" s="9" t="n">
-        <v>0</v>
+      <c r="Z31" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA31" s="10" t="n">
         <v>1</v>
@@ -4471,7 +4471,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4541,8 +4541,8 @@
       <c r="Y37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z37" s="9" t="n">
-        <v>0</v>
+      <c r="Z37" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA37" s="10" t="n">
         <v>1</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4731,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="S39" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T39" s="10" t="n">
         <v>1</v>
@@ -4751,8 +4751,8 @@
       <c r="Y39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z39" s="9" t="n">
-        <v>0</v>
+      <c r="Z39" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA39" s="10" t="n">
         <v>1</v>
@@ -4984,19 +4984,19 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>28677715</v>
+        <v>28679713</v>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>BNP Paribas Porto</t>
+          <t>Vimaranes Toastmasters</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -5010,25 +5010,25 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K42" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M42" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O42" s="7" t="inlineStr">
@@ -5066,15 +5066,13 @@
       <c r="Y42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB42" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="Z42" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA42" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB42" s="4" t="n"/>
       <c r="AC42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
@@ -5089,98 +5087,94 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>7472207</v>
+        <v>28677715</v>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Douro Toastmasters Club</t>
+          <t>BNP Paribas Porto</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M43" s="8" t="n">
+        <v>46387</v>
+      </c>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>Officer list on time</t>
+        </is>
+      </c>
+      <c r="O43" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F43" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I43" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="J43" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="K43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M43" s="8" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N43" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O43" s="7" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T43" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z43" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA43" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB43" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC43" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+      <c r="AC43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -5194,15 +5188,15 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>28680299</v>
+        <v>7472207</v>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Gaia Toastmasters</t>
+          <t>Douro Toastmasters Club</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -5216,10 +5210,10 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K44" s="4" t="n">
         <v>1</v>
@@ -5252,10 +5246,10 @@
         <v>0</v>
       </c>
       <c r="S44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T44" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U44" s="9" t="n">
         <v>0</v>
@@ -5279,9 +5273,13 @@
         <v>1</v>
       </c>
       <c r="AB44" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC44" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC44" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -5295,15 +5293,15 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>3743181</v>
+        <v>28680299</v>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Invicta Toastmasters Club</t>
+          <t>Gaia Toastmasters</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5317,10 +5315,10 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="K45" s="4" t="n">
         <v>1</v>
@@ -5344,7 +5342,7 @@
         </is>
       </c>
       <c r="P45" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q45" s="9" t="n">
         <v>0</v>
@@ -5355,11 +5353,11 @@
       <c r="S45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T45" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U45" s="10" t="n">
-        <v>2</v>
+      <c r="T45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V45" s="9" t="n">
         <v>1</v>
@@ -5368,7 +5366,7 @@
         <v>0</v>
       </c>
       <c r="X45" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y45" s="9" t="n">
         <v>0</v>
@@ -5380,13 +5378,9 @@
         <v>1</v>
       </c>
       <c r="AB45" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC45" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -5400,15 +5394,15 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>28678976</v>
+        <v>3743181</v>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>It´s our turn to Toast</t>
+          <t>Invicta Toastmasters Club</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5422,17 +5416,17 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M46" s="8" t="n">
@@ -5449,7 +5443,7 @@
         </is>
       </c>
       <c r="P46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q46" s="9" t="n">
         <v>0</v>
@@ -5460,34 +5454,38 @@
       <c r="S46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" s="9" t="n">
-        <v>0</v>
+      <c r="T46" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X46" s="9" t="n">
-        <v>1</v>
+      <c r="X46" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z46" s="9" t="n">
-        <v>0</v>
+      <c r="Z46" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA46" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB46" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC46" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC46" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -5497,19 +5495,19 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>28676497</v>
+        <v>28678976</v>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Agueda Toastmasters Club</t>
+          <t>It´s our turn to Toast</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5523,10 +5521,10 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="K47" s="4" t="n">
         <v>0</v>
@@ -5550,7 +5548,7 @@
         </is>
       </c>
       <c r="P47" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q47" s="9" t="n">
         <v>0</v>
@@ -5573,20 +5571,20 @@
       <c r="W47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X47" s="10" t="n">
-        <v>6</v>
+      <c r="X47" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" s="9" t="n">
-        <v>0</v>
+      <c r="Z47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA47" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB47" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AC47" s="4" t="inlineStr"/>
     </row>
@@ -5602,15 +5600,15 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>6786554</v>
+        <v>28676497</v>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Cantanhede Toastmasters Club</t>
+          <t>Agueda Toastmasters Club</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5624,10 +5622,10 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K48" s="4" t="n">
         <v>0</v>
@@ -5651,7 +5649,7 @@
         </is>
       </c>
       <c r="P48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q48" s="9" t="n">
         <v>0</v>
@@ -5675,25 +5673,21 @@
         <v>0</v>
       </c>
       <c r="X48" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z48" s="9" t="n">
-        <v>0</v>
+      <c r="Z48" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA48" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB48" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC48" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="AC48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -5707,15 +5701,15 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>1495468</v>
+        <v>6786554</v>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Clube Toastmasters De Aveiro (CLUTA)</t>
+          <t>Cantanhede Toastmasters Club</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5729,17 +5723,17 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M49" s="8" t="n">
@@ -5756,7 +5750,7 @@
         </is>
       </c>
       <c r="P49" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q49" s="9" t="n">
         <v>0</v>
@@ -5764,17 +5758,17 @@
       <c r="R49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S49" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T49" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U49" s="10" t="n">
-        <v>1</v>
+      <c r="S49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V49" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W49" s="9" t="n">
         <v>0</v>
@@ -5792,11 +5786,11 @@
         <v>1</v>
       </c>
       <c r="AB49" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC49" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -5812,39 +5806,39 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>28675877</v>
+        <v>1495468</v>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Science Toastmasters Club</t>
+          <t>Clube Toastmasters De Aveiro (CLUTA)</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J50" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="K50" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F50" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G50" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I50" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="J50" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="K50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M50" s="8" t="n">
@@ -5861,7 +5855,7 @@
         </is>
       </c>
       <c r="P50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q50" s="9" t="n">
         <v>0</v>
@@ -5869,23 +5863,23 @@
       <c r="R50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S50" s="9" t="n">
-        <v>0</v>
+      <c r="S50" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T50" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U50" s="9" t="n">
-        <v>0</v>
+      <c r="U50" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V50" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X50" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y50" s="9" t="n">
         <v>0</v>
@@ -5897,9 +5891,13 @@
         <v>1</v>
       </c>
       <c r="AB50" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC50" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC50" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -5913,15 +5911,15 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>28679740</v>
+        <v>28675877</v>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Viseu Toastmasters Club</t>
+          <t>Science Toastmasters Club</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5935,17 +5933,17 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="K51" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L51" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M51" s="8" t="n">
@@ -5973,8 +5971,8 @@
       <c r="S51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T51" s="9" t="n">
-        <v>0</v>
+      <c r="T51" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U51" s="9" t="n">
         <v>0</v>
@@ -5986,7 +5984,7 @@
         <v>0</v>
       </c>
       <c r="X51" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y51" s="9" t="n">
         <v>0</v>
@@ -5998,7 +5996,7 @@
         <v>1</v>
       </c>
       <c r="AB51" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AC51" s="4" t="inlineStr"/>
     </row>
@@ -6010,15 +6008,15 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>1570181</v>
+        <v>28679740</v>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Coimbra Toastmasters Club</t>
+          <t>Viseu Toastmasters Club</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
@@ -6036,17 +6034,17 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L52" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M52" s="8" t="n">
@@ -6074,32 +6072,32 @@
       <c r="S52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T52" s="10" t="n">
-        <v>1</v>
+      <c r="T52" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U52" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V52" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W52" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X52" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z52" s="9" t="n">
-        <v>0</v>
+      <c r="Z52" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA52" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB52" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC52" s="4" t="inlineStr"/>
     </row>
@@ -6115,15 +6113,15 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>2154508</v>
+        <v>1570181</v>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Leiria Toastmasters Club</t>
+          <t>Coimbra Toastmasters Club</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6137,17 +6135,17 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M53" s="8" t="n">
@@ -6164,7 +6162,7 @@
         </is>
       </c>
       <c r="P53" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q53" s="9" t="n">
         <v>0</v>
@@ -6175,14 +6173,14 @@
       <c r="S53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T53" s="9" t="n">
-        <v>0</v>
+      <c r="T53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U53" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>0</v>
@@ -6200,13 +6198,9 @@
         <v>1</v>
       </c>
       <c r="AB53" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC53" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -6220,15 +6214,15 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>6954460</v>
+        <v>2154508</v>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Porto De Mos Toastmasters Club</t>
+          <t>Leiria Toastmasters Club</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -6242,25 +6236,25 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="K54" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L54" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M54" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O54" s="7" t="inlineStr">
@@ -6269,7 +6263,7 @@
         </is>
       </c>
       <c r="P54" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q54" s="9" t="n">
         <v>0</v>
@@ -6292,22 +6286,26 @@
       <c r="W54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X54" s="9" t="n">
-        <v>0</v>
+      <c r="X54" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z54" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA54" s="9" t="n">
-        <v>0</v>
+      <c r="Z54" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA54" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB54" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC54" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC54" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -6321,116 +6319,116 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>5149500</v>
+        <v>6954460</v>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Torres Novas Toastmasters Club</t>
+          <t>Porto De Mos Toastmasters Club</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J55" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M55" s="8" t="n">
+        <v>46387</v>
+      </c>
+      <c r="N55" s="4" t="inlineStr">
+        <is>
+          <t>Officer list on time</t>
+        </is>
+      </c>
+      <c r="O55" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB55" s="4" t="n">
         <v>4</v>
-      </c>
-      <c r="F55" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G55" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I55" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="J55" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="K55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M55" s="8" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N55" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O55" s="7" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P55" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q55" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R55" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z55" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA55" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB55" s="4" t="n">
-        <v>5</v>
       </c>
       <c r="AC55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>28678027</v>
+        <v>5149500</v>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Clube Toastmaster Galp</t>
+          <t>Torres Novas Toastmasters Club</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6444,17 +6442,17 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="K56" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L56" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M56" s="8" t="n">
@@ -6473,17 +6471,17 @@
       <c r="P56" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q56" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" s="9" t="n">
-        <v>0</v>
+      <c r="Q56" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R56" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S56" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T56" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="T56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U56" s="9" t="n">
         <v>0</v>
@@ -6495,19 +6493,19 @@
         <v>0</v>
       </c>
       <c r="X56" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y56" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA56" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB56" s="4" t="n">
         <v>5</v>
-      </c>
-      <c r="Y56" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z56" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA56" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB56" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="AC56" s="4" t="inlineStr"/>
     </row>
@@ -6523,15 +6521,15 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>28678396</v>
+        <v>28678027</v>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Inoweiser Toastmasters</t>
+          <t>Clube Toastmaster Galp</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6545,17 +6543,17 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K57" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L57" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M57" s="8" t="n">
@@ -6572,7 +6570,7 @@
         </is>
       </c>
       <c r="P57" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q57" s="9" t="n">
         <v>0</v>
@@ -6581,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="S57" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T57" s="9" t="n">
         <v>0</v>
@@ -6595,20 +6593,20 @@
       <c r="W57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X57" s="9" t="n">
-        <v>2</v>
+      <c r="X57" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z57" s="9" t="n">
-        <v>0</v>
+      <c r="Z57" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA57" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB57" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AC57" s="4" t="inlineStr"/>
     </row>
@@ -6624,15 +6622,15 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>2394775</v>
+        <v>28678396</v>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Lisbon MBA Toastmasters</t>
+          <t>Inoweiser Toastmasters</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6646,17 +6644,17 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L58" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M58" s="8" t="n">
@@ -6691,31 +6689,27 @@
         <v>0</v>
       </c>
       <c r="V58" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="W58" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X58" s="10" t="n">
-        <v>4</v>
-      </c>
       <c r="Y58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z58" s="10" t="n">
-        <v>1</v>
+      <c r="Z58" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA58" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB58" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC58" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="AC58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -6729,11 +6723,11 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>758337</v>
+        <v>2394775</v>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Lisbon Toastmasters Club</t>
+          <t>Lisbon MBA Toastmasters</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
@@ -6751,13 +6745,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -6787,7 +6781,7 @@
         <v>0</v>
       </c>
       <c r="S59" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T59" s="9" t="n">
         <v>0</v>
@@ -6796,13 +6790,13 @@
         <v>0</v>
       </c>
       <c r="V59" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X59" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y59" s="9" t="n">
         <v>0</v>
@@ -6814,11 +6808,11 @@
         <v>1</v>
       </c>
       <c r="AB59" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC59" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -6834,15 +6828,15 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>5488304</v>
+        <v>758337</v>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>PM Portugal Toastmasters</t>
+          <t>Lisbon Toastmasters Club</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6856,13 +6850,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
@@ -6883,25 +6877,25 @@
         </is>
       </c>
       <c r="P60" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q60" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q60" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R60" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S60" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T60" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U60" s="10" t="n">
-        <v>1</v>
+      <c r="T60" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V60" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W60" s="9" t="n">
         <v>0</v>
@@ -6935,19 +6929,19 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>2929225</v>
+        <v>5488304</v>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Almada Communication Leaders</t>
+          <t>PM Portugal Toastmasters</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6961,13 +6955,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
@@ -6988,25 +6982,25 @@
         </is>
       </c>
       <c r="P61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q61" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="S61" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T61" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U61" s="9" t="n">
-        <v>0</v>
+      <c r="U61" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V61" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W61" s="9" t="n">
         <v>0</v>
@@ -7044,15 +7038,15 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>2897675</v>
+        <v>2929225</v>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Lisboa Oriente Toastmasters</t>
+          <t>Almada Communication Leaders</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -7066,13 +7060,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
@@ -7104,14 +7098,14 @@
       <c r="S62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T62" s="9" t="n">
-        <v>0</v>
+      <c r="T62" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U62" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V62" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
@@ -7122,18 +7116,18 @@
       <c r="Y62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z62" s="9" t="n">
-        <v>0</v>
+      <c r="Z62" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA62" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB62" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC62" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -7149,15 +7143,15 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>5749920</v>
+        <v>2897675</v>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Setubal Toastmasters Club</t>
+          <t>Lisboa Oriente Toastmasters</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -7171,13 +7165,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -7201,7 +7195,7 @@
         <v>0</v>
       </c>
       <c r="Q63" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R63" s="9" t="n">
         <v>0</v>
@@ -7215,8 +7209,8 @@
       <c r="U63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V63" s="10" t="n">
-        <v>4</v>
+      <c r="V63" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
@@ -7234,11 +7228,11 @@
         <v>1</v>
       </c>
       <c r="AB63" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC63" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -7254,15 +7248,15 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>1990617</v>
+        <v>5749920</v>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Vasco da Gama Toastmasters Club</t>
+          <t>Setubal Toastmasters Club</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -7276,17 +7270,17 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L64" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M64" s="8" t="n">
@@ -7303,10 +7297,10 @@
         </is>
       </c>
       <c r="P64" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R64" s="9" t="n">
         <v>0</v>
@@ -7314,14 +7308,14 @@
       <c r="S64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T64" s="9" t="n">
-        <v>0</v>
+      <c r="T64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V64" s="9" t="n">
-        <v>1</v>
+      <c r="V64" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
@@ -7339,9 +7333,13 @@
         <v>1</v>
       </c>
       <c r="AB64" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC64" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC64" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -7351,15 +7349,15 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>1425176</v>
+        <v>1990617</v>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Business Speakers Toastmasters Club</t>
+          <t>Vasco da Gama Toastmasters Club</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
@@ -7377,17 +7375,17 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L65" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M65" s="8" t="n">
@@ -7404,10 +7402,10 @@
         </is>
       </c>
       <c r="P65" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q65" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R65" s="9" t="n">
         <v>0</v>
@@ -7422,7 +7420,7 @@
         <v>0</v>
       </c>
       <c r="V65" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
@@ -7440,13 +7438,9 @@
         <v>1</v>
       </c>
       <c r="AB65" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC65" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -7460,15 +7454,15 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>28679015</v>
+        <v>1425176</v>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Ericeira Toastmasters Club</t>
+          <t>Business Speakers Toastmasters Club</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7482,13 +7476,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
@@ -7512,7 +7506,7 @@
         <v>0</v>
       </c>
       <c r="Q66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R66" s="9" t="n">
         <v>0</v>
@@ -7527,29 +7521,29 @@
         <v>0</v>
       </c>
       <c r="V66" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X66" s="9" t="n">
-        <v>3</v>
+      <c r="X66" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z66" s="9" t="n">
-        <v>0</v>
+      <c r="Z66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA66" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB66" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC66" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -7565,15 +7559,15 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>4023798</v>
+        <v>28679015</v>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>International Speakers</t>
+          <t>Ericeira Toastmasters Club</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7587,13 +7581,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
@@ -7614,45 +7608,49 @@
         </is>
       </c>
       <c r="P67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X67" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q67" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R67" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S67" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T67" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V67" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W67" s="10" t="n">
+      <c r="Y67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA67" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB67" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="X67" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y67" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z67" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA67" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB67" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC67" s="4" t="inlineStr"/>
+      <c r="AC67" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -7666,15 +7664,15 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>4515079</v>
+        <v>4023798</v>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Leadership Toastmasters Club</t>
+          <t>International Speakers</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7688,17 +7686,17 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="J68" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="J68" s="4" t="n">
-        <v>14</v>
-      </c>
       <c r="K68" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L68" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>9</v>
+      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M68" s="8" t="n">
@@ -7715,10 +7713,10 @@
         </is>
       </c>
       <c r="P68" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R68" s="9" t="n">
         <v>0</v>
@@ -7732,26 +7730,26 @@
       <c r="U68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V68" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W68" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X68" s="9" t="n">
-        <v>3</v>
+      <c r="V68" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W68" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="X68" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z68" s="9" t="n">
-        <v>0</v>
+      <c r="Z68" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA68" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB68" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AC68" s="4" t="inlineStr"/>
     </row>
@@ -7767,11 +7765,11 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>3263044</v>
+        <v>4515079</v>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>O'VALLEY Toastmasters Club</t>
+          <t>Leadership Toastmasters Club</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
@@ -7789,13 +7787,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -7803,11 +7801,11 @@
         </is>
       </c>
       <c r="M69" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N69" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O69" s="7" t="inlineStr">
@@ -7816,7 +7814,7 @@
         </is>
       </c>
       <c r="P69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q69" s="9" t="n">
         <v>0</v>
@@ -7834,13 +7832,13 @@
         <v>0</v>
       </c>
       <c r="V69" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X69" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y69" s="9" t="n">
         <v>0</v>
@@ -7848,11 +7846,11 @@
       <c r="Z69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA69" s="9" t="n">
-        <v>0</v>
+      <c r="AA69" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB69" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AC69" s="4" t="inlineStr"/>
     </row>
@@ -7864,19 +7862,19 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>28676610</v>
+        <v>3263044</v>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>BNPParibas Portugal</t>
+          <t>O'VALLEY Toastmasters Club</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7890,10 +7888,10 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>0</v>
@@ -7904,11 +7902,11 @@
         </is>
       </c>
       <c r="M70" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N70" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O70" s="7" t="inlineStr">
@@ -7917,10 +7915,10 @@
         </is>
       </c>
       <c r="P70" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q70" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R70" s="9" t="n">
         <v>0</v>
@@ -7946,14 +7944,14 @@
       <c r="Y70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z70" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA70" s="10" t="n">
-        <v>1</v>
+      <c r="Z70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB70" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC70" s="4" t="inlineStr"/>
     </row>
@@ -7965,15 +7963,15 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>28676304</v>
+        <v>28681014</v>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Cisco Portugal Toastmasters Club</t>
+          <t>Sao Tome and Principe Toastmasters</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">
@@ -7991,13 +7989,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
@@ -8036,13 +8034,13 @@
         <v>0</v>
       </c>
       <c r="V71" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X71" s="10" t="n">
-        <v>6</v>
+      <c r="X71" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y71" s="9" t="n">
         <v>0</v>
@@ -8053,14 +8051,8 @@
       <c r="AA71" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB71" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC71" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="AB71" s="4" t="n"/>
+      <c r="AC71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -8074,15 +8066,15 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>28677624</v>
+        <v>28676610</v>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>MPG</t>
+          <t>BNPParibas Portugal</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -8096,10 +8088,10 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K72" s="4" t="n">
         <v>0</v>
@@ -8123,10 +8115,10 @@
         </is>
       </c>
       <c r="P72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R72" s="9" t="n">
         <v>0</v>
@@ -8152,8 +8144,8 @@
       <c r="Y72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z72" s="9" t="n">
-        <v>0</v>
+      <c r="Z72" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA72" s="10" t="n">
         <v>1</v>
@@ -8175,15 +8167,15 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>1361615</v>
+        <v>28676304</v>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Young Entrepreneurs Toastmasters Club</t>
+          <t>Cisco Portugal Toastmasters Club</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8197,13 +8189,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
@@ -8235,14 +8227,14 @@
       <c r="S73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T73" s="10" t="n">
-        <v>1</v>
+      <c r="T73" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U73" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V73" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
@@ -8260,11 +8252,11 @@
         <v>1</v>
       </c>
       <c r="AB73" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC73" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -8276,15 +8268,15 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>2309332</v>
+        <v>28677624</v>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Algarve Toastmasters Club</t>
+          <t>MPG</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
@@ -8302,10 +8294,10 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K74" s="4" t="n">
         <v>0</v>
@@ -8352,8 +8344,8 @@
       <c r="W74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X74" s="10" t="n">
-        <v>6</v>
+      <c r="X74" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y74" s="9" t="n">
         <v>0</v>
@@ -8377,19 +8369,19 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>7871515</v>
+        <v>1361615</v>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Bissau Toastmasters Club</t>
+          <t>Young Entrepreneurs Toastmasters Club</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -8403,17 +8395,17 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="K75" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L75" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L75" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M75" s="8" t="n">
@@ -8441,8 +8433,8 @@
       <c r="S75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T75" s="9" t="n">
-        <v>0</v>
+      <c r="T75" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U75" s="9" t="n">
         <v>0</v>
@@ -8454,23 +8446,23 @@
         <v>0</v>
       </c>
       <c r="X75" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z75" s="9" t="n">
-        <v>0</v>
+      <c r="Z75" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA75" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB75" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC75" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -8486,11 +8478,11 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>28675807</v>
+        <v>2309332</v>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Cabo Verde Toastmasters Speakers</t>
+          <t>Algarve Toastmasters Club</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
@@ -8508,10 +8500,10 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K76" s="4" t="n">
         <v>0</v>
@@ -8571,13 +8563,9 @@
         <v>1</v>
       </c>
       <c r="AB76" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC76" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AC76" s="4" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -8591,15 +8579,15 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>3651492</v>
+        <v>7871515</v>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Portimao Toastmasters Club</t>
+          <t>Bissau Toastmasters Club</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8613,13 +8601,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8640,7 +8628,7 @@
         </is>
       </c>
       <c r="P77" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q77" s="9" t="n">
         <v>0</v>
@@ -8651,20 +8639,20 @@
       <c r="S77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T77" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U77" s="10" t="n">
-        <v>1</v>
+      <c r="T77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W77" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X77" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y77" s="9" t="n">
         <v>0</v>
@@ -8676,7 +8664,7 @@
         <v>1</v>
       </c>
       <c r="AB77" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC77" s="4" t="inlineStr">
         <is>
@@ -8687,24 +8675,24 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>5183</v>
+        <v>28675807</v>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Achievers Club</t>
+          <t>Cabo Verde Toastmasters Speakers</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8718,17 +8706,17 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L78" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M78" s="8" t="n">
@@ -8756,14 +8744,14 @@
       <c r="S78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T78" s="9" t="n">
-        <v>0</v>
+      <c r="T78" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U78" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V78" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
@@ -8781,7 +8769,7 @@
         <v>1</v>
       </c>
       <c r="AB78" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC78" s="4" t="inlineStr">
         <is>
@@ -8792,24 +8780,24 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>28677640</v>
+        <v>3651492</v>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Costa del Soul Speakers Toastmasters</t>
+          <t>Portimao Toastmasters Club</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8823,17 +8811,17 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K79" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L79" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L79" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M79" s="8" t="n">
@@ -8852,8 +8840,8 @@
       <c r="P79" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q79" s="10" t="n">
-        <v>2</v>
+      <c r="Q79" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R79" s="9" t="n">
         <v>0</v>
@@ -8861,11 +8849,11 @@
       <c r="S79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T79" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U79" s="9" t="n">
-        <v>0</v>
+      <c r="T79" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V79" s="9" t="n">
         <v>0</v>
@@ -8874,7 +8862,7 @@
         <v>0</v>
       </c>
       <c r="X79" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y79" s="9" t="n">
         <v>0</v>
@@ -8886,7 +8874,7 @@
         <v>1</v>
       </c>
       <c r="AB79" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC79" s="4" t="inlineStr">
         <is>
@@ -8906,11 +8894,11 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>5202793</v>
+        <v>5183</v>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Oracle Malaga</t>
+          <t>Achievers Club</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
@@ -8928,13 +8916,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
@@ -8955,31 +8943,31 @@
         </is>
       </c>
       <c r="P80" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q80" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R80" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S80" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T80" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U80" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V80" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X80" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y80" s="9" t="n">
         <v>0</v>
@@ -8991,11 +8979,11 @@
         <v>1</v>
       </c>
       <c r="AB80" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC80" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -9011,15 +8999,15 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>28676173</v>
+        <v>28677640</v>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>PowerTalks Malaga</t>
+          <t>Costa del Soul Speakers Toastmasters</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -9033,10 +9021,10 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>0</v>
@@ -9060,10 +9048,10 @@
         </is>
       </c>
       <c r="P81" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q81" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R81" s="9" t="n">
         <v>0</v>
@@ -9084,13 +9072,13 @@
         <v>0</v>
       </c>
       <c r="X81" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z81" s="9" t="n">
-        <v>0</v>
+      <c r="Z81" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA81" s="10" t="n">
         <v>1</v>
@@ -9112,15 +9100,15 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>7367929</v>
+        <v>5202793</v>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Amigos Toastmasters</t>
+          <t>Oracle Malaga</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
@@ -9138,17 +9126,17 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L82" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L82" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M82" s="8" t="n">
@@ -9165,10 +9153,10 @@
         </is>
       </c>
       <c r="P82" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R82" s="9" t="n">
         <v>0</v>
@@ -9183,13 +9171,13 @@
         <v>0</v>
       </c>
       <c r="V82" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W82" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X82" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y82" s="9" t="n">
         <v>0</v>
@@ -9200,8 +9188,14 @@
       <c r="AA82" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB82" s="4" t="n"/>
-      <c r="AC82" s="4" t="inlineStr"/>
+      <c r="AB82" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC82" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -9211,19 +9205,19 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>5832391</v>
+        <v>28676173</v>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Granada</t>
+          <t>PowerTalks Malaga</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -9237,10 +9231,10 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K83" s="4" t="n">
         <v>0</v>
@@ -9264,7 +9258,7 @@
         </is>
       </c>
       <c r="P83" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q83" s="9" t="n">
         <v>0</v>
@@ -9273,10 +9267,10 @@
         <v>0</v>
       </c>
       <c r="S83" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T83" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T83" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U83" s="9" t="n">
         <v>0</v>
@@ -9293,18 +9287,18 @@
       <c r="Y83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z83" s="10" t="n">
-        <v>1</v>
+      <c r="Z83" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA83" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB83" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC83" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -9320,39 +9314,39 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>1578352</v>
+        <v>7367929</v>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Malaga</t>
+          <t>Amigos Toastmasters</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F84" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="J84" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K84" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F84" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G84" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I84" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="J84" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="K84" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L84" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L84" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M84" s="8" t="n">
@@ -9369,16 +9363,16 @@
         </is>
       </c>
       <c r="P84" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q84" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R84" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S84" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T84" s="10" t="n">
         <v>1</v>
@@ -9386,11 +9380,11 @@
       <c r="U84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V84" s="10" t="n">
-        <v>4</v>
+      <c r="V84" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="W84" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X84" s="10" t="n">
         <v>7</v>
@@ -9404,14 +9398,8 @@
       <c r="AA84" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB84" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC84" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+      <c r="AB84" s="4" t="n"/>
+      <c r="AC84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -9425,11 +9413,11 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>2339970</v>
+        <v>5832391</v>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Sevilla</t>
+          <t>Toastmasters Granada</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
@@ -9447,10 +9435,10 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="K85" s="4" t="n">
         <v>0</v>
@@ -9474,16 +9462,16 @@
         </is>
       </c>
       <c r="P85" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q85" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T85" s="10" t="n">
         <v>1</v>
@@ -9498,7 +9486,7 @@
         <v>0</v>
       </c>
       <c r="X85" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y85" s="9" t="n">
         <v>0</v>
@@ -9526,19 +9514,19 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>7799544</v>
+        <v>1578352</v>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>ALC El Jadida Toastmasters</t>
+          <t>Toastmasters Malaga</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9552,17 +9540,17 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L86" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L86" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M86" s="8" t="n">
@@ -9579,45 +9567,49 @@
         </is>
       </c>
       <c r="P86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R86" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S86" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V86" s="9" t="n">
-        <v>1</v>
+      <c r="V86" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X86" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z86" s="9" t="n">
-        <v>0</v>
+      <c r="Z86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA86" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB86" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC86" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC86" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -9627,15 +9619,15 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>6582709</v>
+        <v>2339970</v>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Casablanca Toastmasters Club</t>
+          <t>Toastmasters Sevilla</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
@@ -9653,13 +9645,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
@@ -9680,31 +9672,31 @@
         </is>
       </c>
       <c r="P87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R87" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S87" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T87" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="T87" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V87" s="10" t="n">
-        <v>4</v>
+      <c r="V87" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X87" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y87" s="9" t="n">
         <v>0</v>
@@ -9736,15 +9728,15 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>28678361</v>
+        <v>7799544</v>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>CFC Toastmasters Club</t>
+          <t>ALC El Jadida Toastmasters</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9758,13 +9750,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9772,11 +9764,11 @@
         </is>
       </c>
       <c r="M88" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N88" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O88" s="7" t="inlineStr">
@@ -9803,25 +9795,25 @@
         <v>0</v>
       </c>
       <c r="V88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X88" s="9" t="n">
-        <v>0</v>
+      <c r="X88" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z88" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA88" s="9" t="n">
-        <v>0</v>
+      <c r="Z88" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA88" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB88" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AC88" s="4" t="inlineStr"/>
     </row>
@@ -9837,15 +9829,15 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>5894368</v>
+        <v>6582709</v>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Rabat Toastmasters Club</t>
+          <t>Casablanca Toastmasters Club</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9859,13 +9851,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
@@ -9886,7 +9878,7 @@
         </is>
       </c>
       <c r="P89" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q89" s="9" t="n">
         <v>0</v>
@@ -9895,7 +9887,7 @@
         <v>0</v>
       </c>
       <c r="S89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T89" s="9" t="n">
         <v>0</v>
@@ -9903,14 +9895,14 @@
       <c r="U89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V89" s="9" t="n">
-        <v>1</v>
+      <c r="V89" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X89" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y89" s="9" t="n">
         <v>0</v>
@@ -9938,19 +9930,19 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>7976330</v>
+        <v>28678361</v>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Agadir Toastmasters Club</t>
+          <t>CFC Toastmasters Club</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9964,25 +9956,25 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L90" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L90" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M90" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N90" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O90" s="7" t="inlineStr">
@@ -9991,10 +9983,10 @@
         </is>
       </c>
       <c r="P90" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q90" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q90" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R90" s="9" t="n">
         <v>0</v>
@@ -10008,23 +10000,23 @@
       <c r="U90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V90" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W90" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="X90" s="10" t="n">
-        <v>7</v>
+      <c r="V90" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W90" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X90" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z90" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA90" s="10" t="n">
-        <v>1</v>
+      <c r="Z90" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA90" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB90" s="4" t="n">
         <v>3</v>
@@ -10039,19 +10031,19 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>28677152</v>
+        <v>5894368</v>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Carthage Toastmasters Club</t>
+          <t>Rabat Toastmasters Club</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -10065,17 +10057,17 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L91" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M91" s="8" t="n">
@@ -10092,7 +10084,7 @@
         </is>
       </c>
       <c r="P91" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q91" s="9" t="n">
         <v>0</v>
@@ -10110,27 +10102,31 @@
         <v>0</v>
       </c>
       <c r="V91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X91" s="9" t="n">
-        <v>3</v>
+      <c r="X91" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z91" s="9" t="n">
-        <v>0</v>
+      <c r="Z91" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA91" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB91" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC91" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC91" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -10144,15 +10140,15 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>28679322</v>
+        <v>7976330</v>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>INJAZ El Djazair Toastmasters Club</t>
+          <t>Agadir Toastmasters Club</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -10166,13 +10162,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
@@ -10180,11 +10176,11 @@
         </is>
       </c>
       <c r="M92" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N92" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O92" s="7" t="inlineStr">
@@ -10193,10 +10189,10 @@
         </is>
       </c>
       <c r="P92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q92" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q92" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R92" s="9" t="n">
         <v>0</v>
@@ -10210,26 +10206,26 @@
       <c r="U92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X92" s="9" t="n">
-        <v>0</v>
+      <c r="V92" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W92" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="X92" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA92" s="9" t="n">
-        <v>0</v>
+      <c r="Z92" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB92" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC92" s="4" t="inlineStr"/>
     </row>
@@ -10245,15 +10241,15 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>28677985</v>
+        <v>28677152</v>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>MKC Toastmasters Club</t>
+          <t>Carthage Toastmasters Club</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -10267,10 +10263,10 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K93" s="4" t="n">
         <v>0</v>
@@ -10281,11 +10277,11 @@
         </is>
       </c>
       <c r="M93" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N93" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O93" s="7" t="inlineStr">
@@ -10318,19 +10314,19 @@
         <v>0</v>
       </c>
       <c r="X93" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z93" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA93" s="9" t="n">
-        <v>0</v>
+      <c r="Z93" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA93" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB93" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC93" s="4" t="inlineStr"/>
     </row>
@@ -10346,97 +10342,299 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
+        <v>28679322</v>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>INJAZ El Djazair Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J94" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K94" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M94" s="8" t="n">
+        <v>46387</v>
+      </c>
+      <c r="N94" s="4" t="inlineStr">
+        <is>
+          <t>Officer list on time</t>
+        </is>
+      </c>
+      <c r="O94" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P94" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U94" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V94" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W94" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X94" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC94" s="4" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="n">
+        <v>28677985</v>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>MKC Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M95" s="8" t="n">
+        <v>46387</v>
+      </c>
+      <c r="N95" s="4" t="inlineStr">
+        <is>
+          <t>Officer list on time</t>
+        </is>
+      </c>
+      <c r="O95" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB95" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC95" s="4" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="n">
         <v>7864253</v>
       </c>
-      <c r="D94" s="4" t="inlineStr">
+      <c r="D96" s="4" t="inlineStr">
         <is>
           <t>Tunis Toastmasters</t>
         </is>
       </c>
-      <c r="E94" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F94" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G94" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H94" s="4" t="inlineStr">
+      <c r="E96" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F96" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
         <is>
           <t>Smedley</t>
         </is>
       </c>
-      <c r="I94" s="4" t="n">
+      <c r="I96" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="J94" s="4" t="n">
+      <c r="J96" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="K94" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" s="7" t="inlineStr">
+      <c r="K96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M94" s="8" t="n">
+      <c r="M96" s="8" t="n">
         <v>46446</v>
       </c>
-      <c r="N94" s="4" t="inlineStr">
+      <c r="N96" s="4" t="inlineStr">
         <is>
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O94" s="7" t="inlineStr">
+      <c r="O96" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
-      <c r="P94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T94" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X94" s="10" t="n">
+      <c r="P96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X96" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Y94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA94" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB94" s="4" t="n">
+      <c r="Y96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA96" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB96" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AC94" s="4" t="inlineStr"/>
+      <c r="AC96" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC94"/>
+  <autoFilter ref="A1:AC96"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10688,7 +10886,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -10721,7 +10919,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -10784,16 +10982,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -10802,7 +11000,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -10820,7 +11018,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -10853,7 +11051,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -10886,7 +11084,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -10919,13 +11117,13 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -10952,7 +11150,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -10982,16 +11180,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -11000,7 +11198,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -11051,7 +11249,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -11117,7 +11315,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -11150,7 +11348,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -11183,7 +11381,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>

--- a/docs/d/107/inyear.xlsx
+++ b/docs/d/107/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 13 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 13 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 22 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 22 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
@@ -1112,11 +1112,11 @@
       <c r="U4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V4" s="9" t="n">
-        <v>0</v>
+      <c r="V4" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W4" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X4" s="10" t="n">
         <v>4</v>
@@ -1173,13 +1173,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>4</v>
       </c>
       <c r="W5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5" s="10" t="n">
         <v>4</v>
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="P6" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q6" s="9" t="n">
         <v>0</v>
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1480,13 +1480,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1</v>
+        <v>-15</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
@@ -1524,8 +1524,8 @@
       <c r="U8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V8" s="9" t="n">
-        <v>1</v>
+      <c r="V8" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>0</v>
@@ -1585,17 +1585,17 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-25</v>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M9" s="8" t="n">
@@ -1686,17 +1686,17 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-24</v>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M10" s="8" t="n">
@@ -1787,17 +1787,17 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M11" s="8" t="n">
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
@@ -1892,13 +1892,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -1993,13 +1993,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -2195,17 +2195,17 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M15" s="8" t="n">
@@ -2300,13 +2300,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -2401,13 +2401,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2506,13 +2506,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         </is>
       </c>
       <c r="P18" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="9" t="n">
         <v>0</v>
@@ -2542,7 +2542,7 @@
         <v>0</v>
       </c>
       <c r="S18" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" s="9" t="n">
         <v>0</v>
@@ -2551,7 +2551,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W18" s="9" t="n">
         <v>0</v>
@@ -2611,17 +2611,17 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M19" s="8" t="n">
@@ -2656,7 +2656,7 @@
         <v>0</v>
       </c>
       <c r="V19" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0</v>
@@ -2716,13 +2716,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>1</v>
       </c>
       <c r="V20" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>0</v>
@@ -2821,13 +2821,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
@@ -2926,17 +2926,17 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M22" s="8" t="n">
@@ -2956,7 +2956,7 @@
         <v>2</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" s="9" t="n">
         <v>0</v>
@@ -3031,13 +3031,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -3132,13 +3132,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -3176,8 +3176,8 @@
       <c r="U24" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V24" s="9" t="n">
-        <v>3</v>
+      <c r="V24" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W24" s="9" t="n">
         <v>0</v>
@@ -3342,17 +3342,17 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M26" s="8" t="n">
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3447,13 +3447,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         </is>
       </c>
       <c r="P27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" s="9" t="n">
         <v>0</v>
@@ -3482,8 +3482,8 @@
       <c r="R27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S27" s="9" t="n">
-        <v>1</v>
+      <c r="S27" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T27" s="10" t="n">
         <v>1</v>
@@ -3492,7 +3492,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
@@ -3552,13 +3552,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
@@ -3657,17 +3657,17 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M29" s="8" t="n">
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3762,17 +3762,17 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M30" s="8" t="n">
@@ -3806,8 +3806,8 @@
       <c r="U30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V30" s="9" t="n">
-        <v>3</v>
+      <c r="V30" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W30" s="9" t="n">
         <v>0</v>
@@ -3867,13 +3867,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -3972,13 +3972,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -4174,13 +4174,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4275,13 +4275,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>1</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" s="9" t="n">
         <v>0</v>
@@ -4320,7 +4320,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>0</v>
@@ -4366,7 +4366,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4380,13 +4380,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
@@ -4424,11 +4424,11 @@
       <c r="U36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V36" s="9" t="n">
-        <v>0</v>
+      <c r="V36" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W36" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X36" s="10" t="n">
         <v>5</v>
@@ -4485,13 +4485,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>0</v>
@@ -4695,17 +4695,17 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M39" s="8" t="n">
@@ -4740,7 +4740,7 @@
         <v>0</v>
       </c>
       <c r="V39" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W39" s="9" t="n">
         <v>0</v>
@@ -4800,17 +4800,17 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M40" s="8" t="n">
@@ -4905,13 +4905,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>1</v>
       </c>
       <c r="V41" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>0</v>
@@ -5010,13 +5010,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>0</v>
       </c>
       <c r="V42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W42" s="9" t="n">
         <v>0</v>
@@ -5210,13 +5210,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5315,13 +5315,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
@@ -5416,13 +5416,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>2</v>
       </c>
       <c r="V46" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -5521,17 +5521,17 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M47" s="8" t="n">
@@ -5566,7 +5566,7 @@
         <v>0</v>
       </c>
       <c r="V47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W47" s="9" t="n">
         <v>0</v>
@@ -5622,13 +5622,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5828,13 +5828,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
@@ -5872,11 +5872,11 @@
       <c r="U50" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V50" s="9" t="n">
-        <v>2</v>
+      <c r="V50" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X50" s="10" t="n">
         <v>7</v>
@@ -5933,13 +5933,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -6034,17 +6034,17 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L52" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M52" s="8" t="n">
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6135,13 +6135,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -6179,8 +6179,8 @@
       <c r="U53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V53" s="9" t="n">
-        <v>1</v>
+      <c r="V53" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>0</v>
@@ -6236,13 +6236,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>0</v>
       </c>
       <c r="V54" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W54" s="9" t="n">
         <v>0</v>
@@ -6341,13 +6341,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         <v>0</v>
       </c>
       <c r="V56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W56" s="9" t="n">
         <v>0</v>
@@ -6529,7 +6529,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6543,13 +6543,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
@@ -6587,11 +6587,11 @@
       <c r="U57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V57" s="9" t="n">
-        <v>0</v>
+      <c r="V57" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W57" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X57" s="10" t="n">
         <v>5</v>
@@ -6644,13 +6644,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6745,13 +6745,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>0</v>
       </c>
       <c r="V59" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6850,13 +6850,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
@@ -6894,11 +6894,11 @@
       <c r="U60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V60" s="9" t="n">
-        <v>0</v>
+      <c r="V60" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W60" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X60" s="10" t="n">
         <v>7</v>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6955,13 +6955,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
@@ -6999,11 +6999,11 @@
       <c r="U61" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V61" s="9" t="n">
-        <v>1</v>
+      <c r="V61" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W61" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X61" s="10" t="n">
         <v>7</v>
@@ -7046,7 +7046,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -7060,13 +7060,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>3</v>
+        <v>-6</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
@@ -7104,11 +7104,11 @@
       <c r="U62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V62" s="9" t="n">
-        <v>3</v>
+      <c r="V62" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X62" s="10" t="n">
         <v>7</v>
@@ -7165,17 +7165,17 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L63" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L63" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M63" s="8" t="n">
@@ -7210,7 +7210,7 @@
         <v>0</v>
       </c>
       <c r="V63" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
@@ -7270,13 +7270,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>4</v>
+        <v>-7</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>4</v>
       </c>
       <c r="W64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X64" s="10" t="n">
         <v>7</v>
@@ -7375,13 +7375,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>0</v>
       </c>
       <c r="V65" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7476,13 +7476,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>3</v>
+        <v>-13</v>
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
@@ -7520,8 +7520,8 @@
       <c r="U66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V66" s="9" t="n">
-        <v>3</v>
+      <c r="V66" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
@@ -7581,17 +7581,17 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L67" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M67" s="8" t="n">
@@ -7686,17 +7686,17 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L68" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>3</v>
+      </c>
+      <c r="L68" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M68" s="8" t="n">
@@ -7734,7 +7734,7 @@
         <v>4</v>
       </c>
       <c r="W68" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X68" s="10" t="n">
         <v>7</v>
@@ -7787,13 +7787,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -7989,13 +7989,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
@@ -8033,8 +8033,8 @@
       <c r="U71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V71" s="9" t="n">
-        <v>0</v>
+      <c r="V71" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W71" s="9" t="n">
         <v>0</v>
@@ -8088,13 +8088,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -8189,13 +8189,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
@@ -8294,13 +8294,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -8395,17 +8395,17 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L75" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-26</v>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M75" s="8" t="n">
@@ -8440,7 +8440,7 @@
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
@@ -8500,13 +8500,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         <v>0</v>
       </c>
       <c r="V76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8601,13 +8601,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8706,13 +8706,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8811,13 +8811,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8916,13 +8916,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
@@ -8960,8 +8960,8 @@
       <c r="U80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V80" s="9" t="n">
-        <v>2</v>
+      <c r="V80" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
@@ -9021,17 +9021,17 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L81" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M81" s="8" t="n">
@@ -9066,7 +9066,7 @@
         <v>0</v>
       </c>
       <c r="V81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W81" s="9" t="n">
         <v>0</v>
@@ -9112,7 +9112,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -9126,13 +9126,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
@@ -9155,8 +9155,8 @@
       <c r="P82" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q82" s="9" t="n">
-        <v>1</v>
+      <c r="Q82" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R82" s="9" t="n">
         <v>0</v>
@@ -9171,7 +9171,7 @@
         <v>0</v>
       </c>
       <c r="V82" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W82" s="9" t="n">
         <v>0</v>
@@ -9231,17 +9231,17 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-18</v>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M83" s="8" t="n">
@@ -9276,7 +9276,7 @@
         <v>0</v>
       </c>
       <c r="V83" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
@@ -9336,13 +9336,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9435,13 +9435,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
@@ -9479,8 +9479,8 @@
       <c r="U85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V85" s="9" t="n">
-        <v>0</v>
+      <c r="V85" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -9540,13 +9540,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>5</v>
+        <v>-12</v>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9689,11 +9689,11 @@
       <c r="U87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V87" s="9" t="n">
-        <v>0</v>
+      <c r="V87" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W87" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X87" s="10" t="n">
         <v>6</v>
@@ -9736,7 +9736,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9750,13 +9750,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9794,11 +9794,11 @@
       <c r="U88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V88" s="9" t="n">
-        <v>1</v>
+      <c r="V88" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X88" s="10" t="n">
         <v>6</v>
@@ -9837,7 +9837,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9851,13 +9851,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>4</v>
+        <v>-7</v>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="P89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q89" s="9" t="n">
         <v>0</v>
@@ -9889,8 +9889,8 @@
       <c r="S89" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T89" s="9" t="n">
-        <v>0</v>
+      <c r="T89" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U89" s="9" t="n">
         <v>0</v>
@@ -9899,7 +9899,7 @@
         <v>4</v>
       </c>
       <c r="W89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X89" s="10" t="n">
         <v>4</v>
@@ -9956,13 +9956,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -10057,13 +10057,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
@@ -10093,7 +10093,7 @@
         <v>0</v>
       </c>
       <c r="S91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T91" s="9" t="n">
         <v>0</v>
@@ -10101,11 +10101,11 @@
       <c r="U91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V91" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W91" s="9" t="n">
-        <v>0</v>
+      <c r="V91" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W91" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X91" s="10" t="n">
         <v>5</v>
@@ -10162,17 +10162,17 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L92" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L92" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M92" s="8" t="n">
@@ -10263,13 +10263,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -10364,17 +10364,17 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L94" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M94" s="8" t="n">
@@ -10566,13 +10566,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>0</v>
       </c>
       <c r="V96" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
@@ -10721,7 +10721,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -10754,7 +10754,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -10769,7 +10769,7 @@
         <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -10802,7 +10802,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -10835,7 +10835,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -10868,7 +10868,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -10886,7 +10886,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -10901,7 +10901,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -10919,7 +10919,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -10934,7 +10934,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -10952,7 +10952,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -11000,7 +11000,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -11033,7 +11033,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -11051,13 +11051,13 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -11084,7 +11084,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -11117,7 +11117,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -11150,7 +11150,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -11165,7 +11165,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -11183,7 +11183,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -11198,7 +11198,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -11231,7 +11231,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -11282,7 +11282,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -11297,7 +11297,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -11315,7 +11315,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -11348,7 +11348,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -11396,7 +11396,7 @@
         <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/107/inyear.xlsx
+++ b/docs/d/107/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/107/inyear.xlsx
+++ b/docs/d/107/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/107/inyear.xlsx
+++ b/docs/d/107/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/107/inyear.xlsx
+++ b/docs/d/107/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/107/inyear.xlsx
+++ b/docs/d/107/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 13 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 13 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 22 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 22 clubs short</t>
         </is>
       </c>
     </row>
@@ -1173,13 +1173,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>4</v>
       </c>
       <c r="W5" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X5" s="10" t="n">
         <v>4</v>
@@ -1480,13 +1480,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-15</v>
+        <v>-11</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>4</v>
       </c>
       <c r="W8" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X8" s="10" t="n">
         <v>4</v>
@@ -2130,7 +2130,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" s="10" t="n">
         <v>1</v>
@@ -2821,13 +2821,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
@@ -3132,13 +3132,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3237,13 +3237,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
@@ -3263,8 +3263,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P25" s="9" t="n">
-        <v>3</v>
+      <c r="P25" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q25" s="9" t="n">
         <v>1</v>
@@ -3281,8 +3281,8 @@
       <c r="U25" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V25" s="9" t="n">
-        <v>1</v>
+      <c r="V25" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W25" s="9" t="n">
         <v>0</v>
@@ -3474,7 +3474,7 @@
         </is>
       </c>
       <c r="P27" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q27" s="9" t="n">
         <v>0</v>
@@ -4366,7 +4366,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4380,13 +4380,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
@@ -4427,8 +4427,8 @@
       <c r="V36" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W36" s="9" t="n">
-        <v>2</v>
+      <c r="W36" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X36" s="10" t="n">
         <v>5</v>
@@ -4485,13 +4485,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>0</v>
       </c>
       <c r="V37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W37" s="9" t="n">
         <v>0</v>
@@ -4695,13 +4695,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6483,8 +6483,8 @@
       <c r="T56" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U56" s="9" t="n">
-        <v>0</v>
+      <c r="U56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V56" s="9" t="n">
         <v>1</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6745,13 +6745,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -6789,8 +6789,8 @@
       <c r="U59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V59" s="9" t="n">
-        <v>3</v>
+      <c r="V59" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6955,13 +6955,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
@@ -7002,8 +7002,8 @@
       <c r="V61" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W61" s="9" t="n">
-        <v>3</v>
+      <c r="W61" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X61" s="10" t="n">
         <v>7</v>
@@ -7256,7 +7256,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -7270,13 +7270,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         </is>
       </c>
       <c r="P64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q64" s="9" t="n">
         <v>1</v>
@@ -7311,8 +7311,8 @@
       <c r="T64" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U64" s="9" t="n">
-        <v>0</v>
+      <c r="U64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V64" s="10" t="n">
         <v>4</v>
@@ -7476,13 +7476,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>-13</v>
+        <v>-11</v>
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>4</v>
       </c>
       <c r="W66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X66" s="10" t="n">
         <v>7</v>
@@ -7581,13 +7581,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7686,17 +7686,17 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L68" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M68" s="8" t="n">
@@ -7734,7 +7734,7 @@
         <v>4</v>
       </c>
       <c r="W68" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X68" s="10" t="n">
         <v>7</v>
@@ -7787,13 +7787,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -8395,13 +8395,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-26</v>
+        <v>-25</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -9021,13 +9021,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
         <v>0</v>
       </c>
       <c r="V81" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W81" s="9" t="n">
         <v>0</v>
@@ -9231,13 +9231,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>-18</v>
+        <v>-11</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>0</v>
       </c>
       <c r="V83" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
@@ -9540,13 +9540,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="P89" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q89" s="9" t="n">
         <v>0</v>
@@ -10886,13 +10886,13 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -10952,7 +10952,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -11084,13 +11084,13 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -11117,7 +11117,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -11150,7 +11150,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -11198,7 +11198,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">

--- a/docs/d/107/inyear.xlsx
+++ b/docs/d/107/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 13 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 13 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 22 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 22 clubs short</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
@@ -1115,8 +1115,8 @@
       <c r="V4" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W4" s="9" t="n">
-        <v>3</v>
+      <c r="W4" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X4" s="10" t="n">
         <v>4</v>
@@ -1173,13 +1173,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>4</v>
       </c>
       <c r="W5" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X5" s="10" t="n">
         <v>4</v>
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1304,8 +1304,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P6" s="9" t="n">
-        <v>3</v>
+      <c r="P6" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q6" s="9" t="n">
         <v>0</v>
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -2031,8 +2031,8 @@
       <c r="S13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T13" s="9" t="n">
-        <v>0</v>
+      <c r="T13" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U13" s="9" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
         <v>1</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" s="9" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
         </is>
       </c>
       <c r="P18" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="9" t="n">
         <v>0</v>
@@ -2611,17 +2611,17 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L19" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M19" s="8" t="n">
@@ -2821,13 +2821,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
@@ -2926,17 +2926,17 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L22" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-6</v>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M22" s="8" t="n">
@@ -3474,7 +3474,7 @@
         </is>
       </c>
       <c r="P27" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q27" s="9" t="n">
         <v>0</v>
@@ -3552,13 +3552,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P28" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q28" s="9" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
         <v>4</v>
       </c>
       <c r="W28" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X28" s="10" t="n">
         <v>4</v>
@@ -3867,13 +3867,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -4800,17 +4800,17 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>-10</v>
-      </c>
-      <c r="L40" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-7</v>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M40" s="8" t="n">
@@ -4845,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="V40" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40" s="9" t="n">
         <v>0</v>
@@ -4905,13 +4905,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>0</v>
       </c>
       <c r="S41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T41" s="10" t="n">
         <v>1</v>
@@ -4950,7 +4950,7 @@
         <v>1</v>
       </c>
       <c r="V41" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>0</v>
@@ -5933,13 +5933,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>0</v>
       </c>
       <c r="V51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W51" s="9" t="n">
         <v>0</v>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6162,7 +6162,7 @@
         </is>
       </c>
       <c r="P53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q53" s="9" t="n">
         <v>0</v>
@@ -6176,8 +6176,8 @@
       <c r="T53" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U53" s="9" t="n">
-        <v>0</v>
+      <c r="U53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V53" s="10" t="n">
         <v>4</v>
@@ -6850,13 +6850,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         </is>
       </c>
       <c r="P60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q60" s="9" t="n">
         <v>0</v>
@@ -6898,7 +6898,7 @@
         <v>4</v>
       </c>
       <c r="W60" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X60" s="10" t="n">
         <v>7</v>
@@ -7060,13 +7060,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>4</v>
       </c>
       <c r="W62" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X62" s="10" t="n">
         <v>7</v>
@@ -7165,13 +7165,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7686,13 +7686,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
@@ -7724,8 +7724,8 @@
       <c r="S68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T68" s="9" t="n">
-        <v>0</v>
+      <c r="T68" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U68" s="9" t="n">
         <v>0</v>
@@ -7734,7 +7734,7 @@
         <v>4</v>
       </c>
       <c r="W68" s="10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X68" s="10" t="n">
         <v>7</v>
@@ -9021,13 +9021,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -9231,13 +9231,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9470,8 +9470,8 @@
       <c r="R85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S85" s="9" t="n">
-        <v>1</v>
+      <c r="S85" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T85" s="10" t="n">
         <v>1</v>
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9569,8 +9569,8 @@
       <c r="P86" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q86" s="9" t="n">
-        <v>1</v>
+      <c r="Q86" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R86" s="9" t="n">
         <v>0</v>
@@ -9581,8 +9581,8 @@
       <c r="T86" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U86" s="9" t="n">
-        <v>0</v>
+      <c r="U86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V86" s="10" t="n">
         <v>4</v>
@@ -9631,7 +9631,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9645,13 +9645,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
@@ -9692,8 +9692,8 @@
       <c r="V87" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W87" s="9" t="n">
-        <v>2</v>
+      <c r="W87" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X87" s="10" t="n">
         <v>6</v>
@@ -10566,13 +10566,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -10787,7 +10787,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -10868,7 +10868,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -11000,7 +11000,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -11084,7 +11084,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -11183,7 +11183,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -11315,13 +11315,13 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
